--- a/docs/report-samples/CHIPHI_TEMPLATE_PARTTIME.xlsx
+++ b/docs/report-samples/CHIPHI_TEMPLATE_PARTTIME.xlsx
@@ -140,7 +140,7 @@
     <t>Cột 18 (C44) là khoản CUỐI NĂM: mờ, tách riêng, KHÔNG cộng vào tổng tháng.</t>
   </si>
   <si>
-    <t>Công Ty Tnhh Dược Phẩm Donapharm</t>
+    <t>CÔNG TY CỔ PHẦN DONAPHARM</t>
   </si>
   <si>
     <t>NCL</t>
